--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
@@ -6,11 +6,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Historico" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historico'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$B$7</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-23 17:22</t>
+    <t xml:space="preserve">2026-08-17 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Unidad de medida</t>
   </si>
   <si>
-    <t xml:space="preserve">Crude Migration Index, por 1.000 habitantes</t>
+    <t xml:space="preserve">Índice Bruto de Migración (CMI), por 1.000 habitantes</t>
   </si>
 </sst>
 </file>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 13:37</t>
+    <t xml:space="preserve">2026-08-19 15:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:15</t>
+    <t xml:space="preserve">2026-08-20 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 16:09</t>
+    <t xml:space="preserve">2026-09-03 12:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_valparaiso.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-03 12:22</t>
+    <t xml:space="preserve">2026-09-08 09:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
